--- a/Data Analysis/LW5/betterLife.xlsx
+++ b/Data Analysis/LW5/betterLife.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\studies\Data Analysis\LW5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9142AD1-CF82-49AD-B451-25E340D28020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE2A528-8BDA-48A3-B845-4565BC19AC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="273">
   <si>
     <t>Country</t>
   </si>
@@ -865,6 +865,9 @@
   </si>
   <si>
     <t>y(new)</t>
+  </si>
+  <si>
+    <t>Номер кластера</t>
   </si>
 </sst>
 </file>
@@ -908,7 +911,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -956,11 +959,59 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -976,7 +1027,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -986,11 +1036,120 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="43">
+  <dxfs count="46">
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -1005,31 +1164,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1143,13 +1277,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color theme="9" tint="0.39997558519241921"/>
         </left>
@@ -1159,23 +1286,15 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -1185,55 +1304,18 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color theme="0"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -2571,6 +2653,461 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Диаграмма</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t> рассеяния</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист1!$J$2:$J$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="23"/>
+                <c:pt idx="0">
+                  <c:v>23014</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23319</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>23966</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24194</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25935</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>28407</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>28969</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>29801</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>31855</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>33138</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>34026</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>34045</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>34165</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>47359</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>48531</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>51075</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>53372</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>54291</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>54866</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>55127</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>55536</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>58529</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>59225</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист1!$K$2:$K$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="23"/>
+                <c:pt idx="0">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6.8</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7.9</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.8</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>7.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A5EB-4DE9-BC25-5B2BEC9D2B34}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="436702048"/>
+        <c:axId val="436697056"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="436702048"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="436697056"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="436697056"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="436702048"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2612,6 +3149,46 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3683,20 +4260,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>481012</xdr:rowOff>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>157162</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>42862</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3757,6 +4850,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1000125</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43AEF36A-72AB-4DF3-BF75-46B50A1B987A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3799,76 +4928,76 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A619A8BE-2F18-4988-9B74-408337717188}" name="better_life_index_2024" displayName="better_life_index_2024" ref="A1:Z39" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:Z39" xr:uid="{A619A8BE-2F18-4988-9B74-408337717188}"/>
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{1331DF18-A4BA-403E-85BE-C0916325E8F0}" uniqueName="1" name="Country" queryTableFieldId="1" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{1331DF18-A4BA-403E-85BE-C0916325E8F0}" uniqueName="1" name="Country" queryTableFieldId="1" dataDxfId="45"/>
     <tableColumn id="2" xr3:uid="{46AD8FD4-28E4-4C79-A315-C384B87C7F6A}" uniqueName="2" name="GDP per capita (USD)" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{85407ABE-3ED9-4BFE-93C6-9C2BBF1BE610}" uniqueName="3" name="  Dwellings without basic facilities" queryTableFieldId="3" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{DEE8A53E-F89A-48A0-B913-EDE447C94010}" uniqueName="4" name="  Housing expenditure" queryTableFieldId="4" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{DAC3A24C-D747-4AA7-9AC0-E10849782D78}" uniqueName="5" name="  Rooms per person" queryTableFieldId="5" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{85407ABE-3ED9-4BFE-93C6-9C2BBF1BE610}" uniqueName="3" name="  Dwellings without basic facilities" queryTableFieldId="3" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{DEE8A53E-F89A-48A0-B913-EDE447C94010}" uniqueName="4" name="  Housing expenditure" queryTableFieldId="4" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{DAC3A24C-D747-4AA7-9AC0-E10849782D78}" uniqueName="5" name="  Rooms per person" queryTableFieldId="5" dataDxfId="42"/>
     <tableColumn id="6" xr3:uid="{02153A38-170E-4EF7-B23D-18811F03D109}" uniqueName="6" name="  Household net adjusted disposable income" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{4599EA9C-F196-493E-B4D7-F437FA0A9546}" uniqueName="7" name="  Household net wealth" queryTableFieldId="7"/>
-    <tableColumn id="8" xr3:uid="{72C363F1-FCD2-455E-A8FB-82A781553040}" uniqueName="8" name="  Labour market insecurity" queryTableFieldId="8" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{72C363F1-FCD2-455E-A8FB-82A781553040}" uniqueName="8" name="  Labour market insecurity" queryTableFieldId="8" dataDxfId="41"/>
     <tableColumn id="9" xr3:uid="{DD77C767-F56A-414D-8C5B-71D11D947E84}" uniqueName="9" name="  Employment rate" queryTableFieldId="9"/>
-    <tableColumn id="10" xr3:uid="{58BFEB83-0B60-4291-9C53-F5165439F3A2}" uniqueName="10" name="  Long-term unemployment rate" queryTableFieldId="10" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{58BFEB83-0B60-4291-9C53-F5165439F3A2}" uniqueName="10" name="  Long-term unemployment rate" queryTableFieldId="10" dataDxfId="40"/>
     <tableColumn id="11" xr3:uid="{47D98615-91D8-4420-9DF9-09D0B4436BD4}" uniqueName="11" name="  Personal earnings" queryTableFieldId="11"/>
     <tableColumn id="12" xr3:uid="{DA2B8B88-0427-4773-B1EF-6FE506CC5349}" uniqueName="12" name="  Quality of support network" queryTableFieldId="12"/>
     <tableColumn id="13" xr3:uid="{91682FED-2983-4DE3-AD8F-531C78CFD527}" uniqueName="13" name="  Educational attainment" queryTableFieldId="13"/>
     <tableColumn id="14" xr3:uid="{FF3E8E9F-3DBA-45C7-91B5-C8E32F60555B}" uniqueName="14" name="  Student skills" queryTableFieldId="14"/>
     <tableColumn id="15" xr3:uid="{6CD7DE5C-720B-4FC4-9920-BEBF05D65EDB}" uniqueName="15" name="  Years in education" queryTableFieldId="15"/>
-    <tableColumn id="16" xr3:uid="{9094B064-41D3-487A-A2E9-8C6812DA3B8E}" uniqueName="16" name="  Air pollution" queryTableFieldId="16" dataDxfId="36"/>
+    <tableColumn id="16" xr3:uid="{9094B064-41D3-487A-A2E9-8C6812DA3B8E}" uniqueName="16" name="  Air pollution" queryTableFieldId="16" dataDxfId="39"/>
     <tableColumn id="17" xr3:uid="{70C274FD-6841-4D89-A4F0-B743A1809C5F}" uniqueName="17" name="  Water quality" queryTableFieldId="17"/>
-    <tableColumn id="18" xr3:uid="{B32CA9C9-8CCC-472E-85BB-520641503BB0}" uniqueName="18" name="  Stakeholder engagement for developing regulations" queryTableFieldId="18" dataDxfId="35"/>
+    <tableColumn id="18" xr3:uid="{B32CA9C9-8CCC-472E-85BB-520641503BB0}" uniqueName="18" name="  Stakeholder engagement for developing regulations" queryTableFieldId="18" dataDxfId="38"/>
     <tableColumn id="19" xr3:uid="{19C9FC99-D9E7-4620-B47E-EAC3509BC68F}" uniqueName="19" name="  Voter turnout" queryTableFieldId="19"/>
-    <tableColumn id="20" xr3:uid="{B021955E-74CA-4127-AA30-9825E280A651}" uniqueName="20" name="  Life expectancy" queryTableFieldId="20" dataDxfId="34"/>
+    <tableColumn id="20" xr3:uid="{B021955E-74CA-4127-AA30-9825E280A651}" uniqueName="20" name="  Life expectancy" queryTableFieldId="20" dataDxfId="37"/>
     <tableColumn id="21" xr3:uid="{83CFC343-999B-4039-85C8-1CD98CE1CDAE}" uniqueName="21" name="  Self-reported health" queryTableFieldId="21"/>
     <tableColumn id="22" xr3:uid="{D705E1C0-4745-46C4-95E9-977EE2F4CA88}" uniqueName="22" name="  Feeling safe walking alone at night" queryTableFieldId="22"/>
-    <tableColumn id="23" xr3:uid="{DEDDC73A-1E96-416D-823A-59A8EE04F0A3}" uniqueName="23" name="  Homicide rate" queryTableFieldId="23" dataDxfId="33"/>
-    <tableColumn id="24" xr3:uid="{BCD26029-8494-40E7-B5D4-177BC12EBA76}" uniqueName="24" name="  Employees working very long hours" queryTableFieldId="24" dataDxfId="32"/>
-    <tableColumn id="25" xr3:uid="{A7648DF1-458D-4341-950E-720184ADB0EF}" uniqueName="25" name="  Time devoted to leisure and personal care" queryTableFieldId="25" dataDxfId="31"/>
-    <tableColumn id="26" xr3:uid="{A0E61BAB-711A-448E-A704-1DFD82CFABAF}" uniqueName="26" name="  Life satisfaction" queryTableFieldId="26" dataDxfId="30"/>
+    <tableColumn id="23" xr3:uid="{DEDDC73A-1E96-416D-823A-59A8EE04F0A3}" uniqueName="23" name="  Homicide rate" queryTableFieldId="23" dataDxfId="36"/>
+    <tableColumn id="24" xr3:uid="{BCD26029-8494-40E7-B5D4-177BC12EBA76}" uniqueName="24" name="  Employees working very long hours" queryTableFieldId="24" dataDxfId="35"/>
+    <tableColumn id="25" xr3:uid="{A7648DF1-458D-4341-950E-720184ADB0EF}" uniqueName="25" name="  Time devoted to leisure and personal care" queryTableFieldId="25" dataDxfId="34"/>
+    <tableColumn id="26" xr3:uid="{A0E61BAB-711A-448E-A704-1DFD82CFABAF}" uniqueName="26" name="  Life satisfaction" queryTableFieldId="26" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97CED990-E0AD-4049-9D5C-9EDAE3A0398E}" name="Таблица2" displayName="Таблица2" ref="A1:G39" totalsRowShown="0" headerRowDxfId="29" headerRowBorderDxfId="28" tableBorderDxfId="27" totalsRowBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97CED990-E0AD-4049-9D5C-9EDAE3A0398E}" name="Таблица2" displayName="Таблица2" ref="A1:G39" totalsRowShown="0" headerRowDxfId="32" headerRowBorderDxfId="31" tableBorderDxfId="30" totalsRowBorderDxfId="29">
   <autoFilter ref="A1:G39" xr:uid="{97CED990-E0AD-4049-9D5C-9EDAE3A0398E}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{804D964C-0E40-443F-8354-7E3A6A793E82}" name="Country" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{9D470B8E-97B5-4D07-A7CD-6F42A4DAC2B3}" name="GDP per capita (USD)" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{5CD4D351-DDBF-41AD-9297-7129B9BA1A82}" name="  Life expectancy" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{FF20AAFF-E8B0-4F26-84F8-B4D77D4CCDC0}" name="  Employment rate" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{38326172-D301-4B95-B35D-E9E32D23F670}" name="  Quality of support network" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{76A806F8-1375-4D41-B135-FF8715BCA6CE}" name="  Feeling safe walking alone at night" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{B8AE9B68-9413-4263-A7EF-480763C86177}" name="  Life satisfaction" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{804D964C-0E40-443F-8354-7E3A6A793E82}" name="Country" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{9D470B8E-97B5-4D07-A7CD-6F42A4DAC2B3}" name="GDP per capita (USD)" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{5CD4D351-DDBF-41AD-9297-7129B9BA1A82}" name="  Life expectancy" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{FF20AAFF-E8B0-4F26-84F8-B4D77D4CCDC0}" name="  Employment rate" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{38326172-D301-4B95-B35D-E9E32D23F670}" name="  Quality of support network" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{76A806F8-1375-4D41-B135-FF8715BCA6CE}" name="  Feeling safe walking alone at night" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{B8AE9B68-9413-4263-A7EF-480763C86177}" name="  Life satisfaction" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B3C2ECC0-0555-494A-8A3F-F8B8D9B60462}" name="Таблица4" displayName="Таблица4" ref="I1:P24" totalsRowShown="0" headerRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B3C2ECC0-0555-494A-8A3F-F8B8D9B60462}" name="Таблица4" displayName="Таблица4" ref="I1:P24" totalsRowShown="0" headerRowDxfId="9" dataDxfId="0" headerRowBorderDxfId="21">
   <autoFilter ref="I1:P24" xr:uid="{B3C2ECC0-0555-494A-8A3F-F8B8D9B60462}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I2:K24">
     <sortCondition ref="J1:J24"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{B1B3B9F8-5A55-435B-B4DA-CD990659085B}" name="Country" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{D36138DF-5DFB-4E02-B45F-87411AB02865}" name="GDP per capita (USD)"/>
-    <tableColumn id="3" xr3:uid="{6CF7D397-576F-4E10-8A8A-144466254266}" name="  Life satisfaction" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{A4C67A62-E8AC-4CAD-BAE1-4E84C0D3519D}" name="Расстояние от m1" dataDxfId="15">
+    <tableColumn id="1" xr3:uid="{B1B3B9F8-5A55-435B-B4DA-CD990659085B}" name="Country" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{D36138DF-5DFB-4E02-B45F-87411AB02865}" name="GDP per capita (USD)" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{6CF7D397-576F-4E10-8A8A-144466254266}" name="  Life satisfaction" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{A4C67A62-E8AC-4CAD-BAE1-4E84C0D3519D}" name="Расстояние от m1" dataDxfId="5">
       <calculatedColumnFormula>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7C85FFC9-A81F-47F7-A67B-96F9BFC648F3}" name="Расстояние от m2" dataDxfId="14">
+    <tableColumn id="5" xr3:uid="{7C85FFC9-A81F-47F7-A67B-96F9BFC648F3}" name="Расстояние от m2" dataDxfId="4">
       <calculatedColumnFormula>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{AE1E3811-C893-4F7D-AFB0-3BD292D88716}" name="Принадлежит кластеру" dataDxfId="13">
+    <tableColumn id="6" xr3:uid="{AE1E3811-C893-4F7D-AFB0-3BD292D88716}" name="Принадлежит кластеру" dataDxfId="3">
       <calculatedColumnFormula>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{DF1E96BA-F49E-4F36-8DD1-81800B05FB88}" name="err" dataDxfId="12">
+    <tableColumn id="7" xr3:uid="{DF1E96BA-F49E-4F36-8DD1-81800B05FB88}" name="err" dataDxfId="2">
       <calculatedColumnFormula>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{2C9701F3-C5D2-4CD1-94BC-E0C82C47CFD2}" name="err^2" dataDxfId="11">
+    <tableColumn id="8" xr3:uid="{2C9701F3-C5D2-4CD1-94BC-E0C82C47CFD2}" name="err^2" dataDxfId="1">
       <calculatedColumnFormula>Таблица4[[#This Row],[err]]^2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3877,25 +5006,25 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{756F8DCB-915C-42BB-AE1B-2262F487549E}" name="Таблица5" displayName="Таблица5" ref="I32:P55" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="9" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{756F8DCB-915C-42BB-AE1B-2262F487549E}" name="Таблица5" displayName="Таблица5" ref="I32:P55" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18">
   <autoFilter ref="I32:P55" xr:uid="{756F8DCB-915C-42BB-AE1B-2262F487549E}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{2BC3B326-0951-4590-A7A3-684B4539D7B9}" name="Country" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{FA0DAD67-532B-45E0-8F83-75A188869EFB}" name="GDP per capita (USD)" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{302B04FA-80FC-4B00-811B-252F4C3CDB89}" name="  Life satisfaction" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{BD3A90B9-A67C-4668-A634-60E9C08B54DB}" name="Расстояние от m1" dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{2BC3B326-0951-4590-A7A3-684B4539D7B9}" name="Country" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{FA0DAD67-532B-45E0-8F83-75A188869EFB}" name="GDP per capita (USD)" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{302B04FA-80FC-4B00-811B-252F4C3CDB89}" name="  Life satisfaction" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{BD3A90B9-A67C-4668-A634-60E9C08B54DB}" name="Расстояние от m1" dataDxfId="14">
       <calculatedColumnFormula>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{BFF2DD7C-6755-4B2F-9C76-B9F82822B7D2}" name="Расстояние от m2" dataDxfId="3">
+    <tableColumn id="5" xr3:uid="{BFF2DD7C-6755-4B2F-9C76-B9F82822B7D2}" name="Расстояние от m2" dataDxfId="13">
       <calculatedColumnFormula>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A6D210BD-489D-4129-91AC-C7A8EFF40C3E}" name="Принадлежит кластеру" dataDxfId="2">
+    <tableColumn id="6" xr3:uid="{A6D210BD-489D-4129-91AC-C7A8EFF40C3E}" name="Принадлежит кластеру" dataDxfId="12">
       <calculatedColumnFormula>IF(Таблица5[[#This Row],[Расстояние от m1]]&lt;Таблица5[[#This Row],[Расстояние от m2]],1,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{DDC19E35-9A38-42AE-89CA-93A41679BEE2}" name="err" dataDxfId="1">
+    <tableColumn id="7" xr3:uid="{DDC19E35-9A38-42AE-89CA-93A41679BEE2}" name="err" dataDxfId="11">
       <calculatedColumnFormula>MIN(Таблица5[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{36B53162-3FFC-4924-B009-25FA287E1BAE}" name="err^2" dataDxfId="0">
+    <tableColumn id="8" xr3:uid="{36B53162-3FFC-4924-B009-25FA287E1BAE}" name="err^2" dataDxfId="10">
       <calculatedColumnFormula>Таблица5[[#This Row],[err]]^2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7283,6 +8412,8 @@
     <col min="12" max="13" width="19" customWidth="1"/>
     <col min="14" max="14" width="24.5703125" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.85546875" customWidth="1"/>
+    <col min="19" max="20" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7325,7 +8456,7 @@
       <c r="N1" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="11" t="s">
         <v>267</v>
       </c>
       <c r="P1" s="11" t="s">
@@ -7354,32 +8485,32 @@
       <c r="G2" s="4">
         <v>7.1</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="16">
         <v>23014</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="15">
         <v>6.1</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>11151.000004035513</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>24345.000007393715</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>1</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>11151.000004035513</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>124344801.09000002</v>
       </c>
@@ -7406,32 +8537,32 @@
       <c r="G3" s="5">
         <v>7.2</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="16">
         <v>23319</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="15">
         <v>6</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>10846.000001843999</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>24040.000010191347</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>1</v>
       </c>
-      <c r="O3" s="1">
+      <c r="O3" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>10846.000001843999</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>117635716.04000002</v>
       </c>
@@ -7458,32 +8589,32 @@
       <c r="G4" s="4">
         <v>6.8</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="16">
         <v>23966</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="18">
         <v>5.8</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>10199</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>23393.000017312872</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>1</v>
       </c>
-      <c r="O4" s="1">
+      <c r="O4" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>10199</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>104019601</v>
       </c>
@@ -7510,32 +8641,32 @@
       <c r="G5" s="5">
         <v>7</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="16">
         <v>24194</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="18">
         <v>6.2</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>9971.0000080232676</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>23165.000005396072</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>1</v>
       </c>
-      <c r="O5" s="1">
+      <c r="O5" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>9971.0000080232676</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>99420841.159999996</v>
       </c>
@@ -7562,32 +8693,32 @@
       <c r="G6" s="4">
         <v>6.2</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="16">
         <v>25935</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="15">
         <v>6.5</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>8230.0000297691367</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>21424.000000933534</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>1</v>
       </c>
-      <c r="O6" s="1">
+      <c r="O6" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>8230.0000297691367</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>67732900.489999995</v>
       </c>
@@ -7614,32 +8745,32 @@
       <c r="G7" s="5">
         <v>5.7</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="16">
         <v>28407</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="15">
         <v>6.4</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>5758.0000312608545</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>18952.000002374418</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>1</v>
       </c>
-      <c r="O7" s="1">
+      <c r="O7" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>5758.0000312608545</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P7" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>33154564.359999999</v>
       </c>
@@ -7666,32 +8797,32 @@
       <c r="G8" s="4">
         <v>6.3</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="16">
         <v>28969</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="18">
         <v>5.8</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>5196</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>18390.000022022839</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>1</v>
       </c>
-      <c r="O8" s="1">
+      <c r="O8" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>5196</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P8" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>26998416</v>
       </c>
@@ -7718,32 +8849,32 @@
       <c r="G9" s="5">
         <v>6.9</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="16">
         <v>29801</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="18">
         <v>6.9</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>4364.0001386342783</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>17558.000001139084</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>1</v>
       </c>
-      <c r="O9" s="1">
+      <c r="O9" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>4364.0001386342783</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>19044497.210000001</v>
       </c>
@@ -7770,32 +8901,32 @@
       <c r="G10" s="4">
         <v>7.5</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="16">
         <v>31855</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="18">
         <v>6.5</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>2310.0001060606037</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>15504.000001289989</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>1</v>
       </c>
-      <c r="O10" s="1">
+      <c r="O10" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>2310.0001060606037</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P10" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>5336100.49</v>
       </c>
@@ -7822,32 +8953,32 @@
       <c r="G11" s="5">
         <v>6.5</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="16">
         <v>33138</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11" s="18">
         <v>6.1</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>1027.0000438169416</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>14221.000012657338</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>1</v>
       </c>
-      <c r="O11" s="1">
+      <c r="O11" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>1027.0000438169416</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P11" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>1054729.0899999999</v>
       </c>
@@ -7874,32 +9005,32 @@
       <c r="G12" s="4">
         <v>7.9</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="16">
         <v>34026</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="18">
         <v>6.5</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>139.00176257875293</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>13333.000001500037</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>1</v>
       </c>
-      <c r="O12" s="1">
+      <c r="O12" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>139.00176257875293</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P12" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>19321.489999999998</v>
       </c>
@@ -7926,32 +9057,32 @@
       <c r="G13" s="5">
         <v>6.7</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="16">
         <v>34045</v>
       </c>
-      <c r="K13" s="4">
+      <c r="K13" s="15">
         <v>6.5</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>120.00204164929862</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>13314.000001502178</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>1</v>
       </c>
-      <c r="O13" s="1">
+      <c r="O13" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>120.00204164929862</v>
       </c>
-      <c r="P13" s="1">
+      <c r="P13" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>14400.49</v>
       </c>
@@ -7978,32 +9109,32 @@
       <c r="G14" s="4">
         <v>7.3</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="16">
         <v>34165</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K14" s="15">
         <v>5.8</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>0</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>13194.00003069577</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>1</v>
       </c>
-      <c r="O14" s="1">
+      <c r="O14" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>0</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>0</v>
       </c>
@@ -8030,32 +9161,32 @@
       <c r="G15" s="5">
         <v>5.8</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="16">
         <v>47359</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K15" s="18">
         <v>6.7</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>13194.00003069577</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>0</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>2</v>
       </c>
-      <c r="O15" s="1">
+      <c r="O15" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>0</v>
       </c>
-      <c r="P15" s="1">
+      <c r="P15" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>0</v>
       </c>
@@ -8082,32 +9213,32 @@
       <c r="G16" s="4">
         <v>6</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="16">
         <v>48531</v>
       </c>
-      <c r="K16" s="4">
+      <c r="K16" s="15">
         <v>7.3</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>14366.000078309899</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>1172.0001535836077</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>2</v>
       </c>
-      <c r="O16" s="1">
+      <c r="O16" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>1172.0001535836077</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>1373584.36</v>
       </c>
@@ -8134,32 +9265,32 @@
       <c r="G17" s="5">
         <v>7.6</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="16">
         <v>51075</v>
       </c>
-      <c r="K17" s="4">
+      <c r="K17" s="15">
         <v>6.8</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>16910.000029568302</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>3716.0000013455328</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>2</v>
       </c>
-      <c r="O17" s="1">
+      <c r="O17" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>3716.0000013455328</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P17" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>13808656.01</v>
       </c>
@@ -8186,32 +9317,32 @@
       <c r="G18" s="4">
         <v>7</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="16">
         <v>53372</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K18" s="18">
         <v>7.2</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>19207.000051023064</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>6013.0000207882922</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>2</v>
       </c>
-      <c r="O18" s="1">
+      <c r="O18" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>6013.0000207882922</v>
       </c>
-      <c r="P18" s="1">
+      <c r="P18" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>36156169.25</v>
       </c>
@@ -8238,32 +9369,32 @@
       <c r="G19" s="5">
         <v>7.2</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="16">
         <v>54291</v>
       </c>
-      <c r="K19" s="4">
+      <c r="K19" s="15">
         <v>7.3</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>20126.000055897843</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>6932.0000259665321</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>2</v>
       </c>
-      <c r="O19" s="1">
+      <c r="O19" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>6932.0000259665321</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P19" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>48052624.359999999</v>
       </c>
@@ -8290,32 +9421,32 @@
       <c r="G20" s="4">
         <v>6.5</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="16">
         <v>54866</v>
       </c>
-      <c r="K20" s="5">
+      <c r="K20" s="18">
         <v>7</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>20701.000034780929</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>7507.0000059944059</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>2</v>
       </c>
-      <c r="O20" s="1">
+      <c r="O20" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>7507.0000059944059</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P20" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>56355049.090000011</v>
       </c>
@@ -8342,32 +9473,32 @@
       <c r="G21" s="5">
         <v>6.1</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="16">
         <v>55127</v>
       </c>
-      <c r="K21" s="4">
+      <c r="K21" s="15">
         <v>7.9</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>20962.000105190345</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>7768.0000926879502</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>2</v>
       </c>
-      <c r="O21" s="1">
+      <c r="O21" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>7768.0000926879502</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P21" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>60341825.440000005</v>
       </c>
@@ -8394,32 +9525,32 @@
       <c r="G22" s="4">
         <v>5.8</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="16">
         <v>55536</v>
       </c>
-      <c r="K22" s="4">
+      <c r="K22" s="15">
         <v>6.8</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>21371.000023396191</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>8177.0000006114715</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>2</v>
       </c>
-      <c r="O22" s="1">
+      <c r="O22" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>8177.0000006114715</v>
       </c>
-      <c r="P22" s="1">
+      <c r="P22" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>66863329.010000005</v>
       </c>
@@ -8446,32 +9577,32 @@
       <c r="G23" s="5">
         <v>6.2</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="I23" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="16">
         <v>58529</v>
       </c>
-      <c r="K23" s="5">
+      <c r="K23" s="18">
         <v>7.3</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>24364.000046174682</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>11170.000016114593</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>2</v>
       </c>
-      <c r="O23" s="1">
+      <c r="O23" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>11170.000016114593</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P23" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>124768900.36</v>
       </c>
@@ -8498,39 +9629,42 @@
       <c r="G24" s="4">
         <v>6.4</v>
       </c>
-      <c r="I24" s="5" t="s">
+      <c r="I24" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="16">
         <v>59225</v>
       </c>
-      <c r="K24" s="5">
+      <c r="K24" s="18">
         <v>7.2</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$27)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$27)^2)</f>
         <v>25060.000039106148</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="16">
         <f>SQRT((Таблица4[[#This Row],[GDP per capita (USD)]]-$J$28)^2 + (Таблица4[[#This Row],[  Life satisfaction]]-$K$28)^2)</f>
         <v>11866.000010534299</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="16">
         <f>IF(Таблица4[[#This Row],[Расстояние от m1]]&lt;Таблица4[[#This Row],[Расстояние от m2]],1,2)</f>
         <v>2</v>
       </c>
-      <c r="O24" s="1">
+      <c r="O24" s="17">
         <f>MIN(Таблица4[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
         <v>11866.000010534299</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="17">
         <f>Таблица4[[#This Row],[err]]^2</f>
         <v>140801956.24999997</v>
       </c>
-      <c r="S24" t="s">
+      <c r="R24" s="20" t="s">
+        <v>272</v>
+      </c>
+      <c r="S24" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="T24" t="s">
+      <c r="T24" s="22" t="s">
         <v>271</v>
       </c>
     </row>
@@ -8556,14 +9690,14 @@
       <c r="G25" s="5">
         <v>7.4</v>
       </c>
-      <c r="R25">
+      <c r="R25" s="23">
         <v>1</v>
       </c>
-      <c r="S25">
+      <c r="S25" s="24">
         <f>SUM(J2:J14) / COUNT(J2:J14)</f>
         <v>28833.384615384617</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="25">
         <f>SUM(K2:K14) / COUNT(K2:K14)</f>
         <v>6.2384615384615376</v>
       </c>
@@ -8603,14 +9737,14 @@
         <f>SUM(Таблица4[err^2])</f>
         <v>1147297983.0400002</v>
       </c>
-      <c r="R26">
+      <c r="R26" s="19">
         <v>2</v>
       </c>
-      <c r="S26">
+      <c r="S26" s="3">
         <f>SUM(J15:J24) / COUNT(J15:J24)</f>
         <v>53791.1</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="14">
         <f>SUM(K15:K24) / COUNT(K15:K24)</f>
         <v>7.15</v>
       </c>
@@ -8748,7 +9882,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>225</v>
       </c>
@@ -8788,10 +9922,10 @@
       <c r="N32" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="O32" s="13" t="s">
+      <c r="O32" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="P32" s="14" t="s">
+      <c r="P32" s="13" t="s">
         <v>268</v>
       </c>
     </row>
@@ -8828,7 +9962,7 @@
       </c>
       <c r="L33">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>5819.3846170318357</v>
+        <v>5819.3846170318175</v>
       </c>
       <c r="M33">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -8840,11 +9974,11 @@
       </c>
       <c r="O33" s="1">
         <f>MIN(Таблица5[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
-        <v>5819.3846170318357</v>
+        <v>5819.3846170318175</v>
       </c>
       <c r="P33">
         <f>Таблица5[[#This Row],[err]]^2</f>
-        <v>33865237.320946768</v>
+        <v>33865237.320946552</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -8880,7 +10014,7 @@
       </c>
       <c r="L34">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>5514.384620540578</v>
+        <v>5514.3846205405598</v>
       </c>
       <c r="M34">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -8892,11 +10026,11 @@
       </c>
       <c r="O34">
         <f>MIN(Таблица5[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
-        <v>5514.384620540578</v>
+        <v>5514.3846205405598</v>
       </c>
       <c r="P34">
         <f>Таблица5[[#This Row],[err]]^2</f>
-        <v>30408437.743254453</v>
+        <v>30408437.743254256</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -8932,7 +10066,7 @@
       </c>
       <c r="L35">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>4867.3846351332641</v>
+        <v>4867.3846351332459</v>
       </c>
       <c r="M35">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -8944,11 +10078,11 @@
       </c>
       <c r="O35">
         <f>MIN(Таблица5[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
-        <v>4867.3846351332641</v>
+        <v>4867.3846351332459</v>
       </c>
       <c r="P35">
         <f>Таблица5[[#This Row],[err]]^2</f>
-        <v>23691433.186331376</v>
+        <v>23691433.186331201</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -8984,7 +10118,7 @@
       </c>
       <c r="L36">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>4639.3846155440451</v>
+        <v>4639.384615544026</v>
       </c>
       <c r="M36">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -8996,11 +10130,11 @@
       </c>
       <c r="O36">
         <f>MIN(Таблица5[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
-        <v>4639.3846155440451</v>
+        <v>4639.384615544026</v>
       </c>
       <c r="P36">
         <f>Таблица5[[#This Row],[err]]^2</f>
-        <v>21523889.610946767</v>
+        <v>21523889.610946592</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -9036,7 +10170,7 @@
       </c>
       <c r="L37">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>2898.3846271847015</v>
+        <v>2898.3846271846833</v>
       </c>
       <c r="M37">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9048,11 +10182,11 @@
       </c>
       <c r="O37">
         <f>MIN(Таблица5[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
-        <v>2898.3846271847015</v>
+        <v>2898.3846271846833</v>
       </c>
       <c r="P37">
         <f>Таблица5[[#This Row],[err]]^2</f>
-        <v>8400633.4471006002</v>
+        <v>8400633.4471004959</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
@@ -9088,7 +10222,7 @@
       </c>
       <c r="L38">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>426.38464598454107</v>
+        <v>426.38464598452288</v>
       </c>
       <c r="M38">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9100,11 +10234,11 @@
       </c>
       <c r="O38">
         <f>MIN(Таблица5[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
-        <v>426.38464598454107</v>
+        <v>426.38464598452288</v>
       </c>
       <c r="P38">
         <f>Таблица5[[#This Row],[err]]^2</f>
-        <v>181803.8663313624</v>
+        <v>181803.86633134689</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -9140,7 +10274,7 @@
       </c>
       <c r="L39">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>135.61609341408914</v>
+        <v>135.61609341410733</v>
       </c>
       <c r="M39">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9152,11 +10286,11 @@
       </c>
       <c r="O39">
         <f>MIN(Таблица5[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
-        <v>135.61609341408914</v>
+        <v>135.61609341410733</v>
       </c>
       <c r="P39">
         <f>Таблица5[[#This Row],[err]]^2</f>
-        <v>18391.724792898949</v>
+        <v>18391.724792903886</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
@@ -9171,7 +10305,7 @@
       </c>
       <c r="L40">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>967.61561075538225</v>
+        <v>967.61561075540055</v>
       </c>
       <c r="M40">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9183,11 +10317,11 @@
       </c>
       <c r="O40">
         <f>MIN(Таблица5[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
-        <v>967.61561075538225</v>
+        <v>967.61561075540055</v>
       </c>
       <c r="P40">
         <f>Таблица5[[#This Row],[err]]^2</f>
-        <v>936279.97017751145</v>
+        <v>936279.97017754684</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -9202,7 +10336,7 @@
       </c>
       <c r="L41">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>3021.6153959342237</v>
+        <v>3021.6153959342419</v>
       </c>
       <c r="M41">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9214,11 +10348,11 @@
       </c>
       <c r="O41">
         <f>MIN(Таблица5[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
-        <v>3021.6153959342237</v>
+        <v>3021.6153959342419</v>
       </c>
       <c r="P41">
         <f>Таблица5[[#This Row],[err]]^2</f>
-        <v>9130159.6009467356</v>
+        <v>9130159.6009468455</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -9233,7 +10367,7 @@
       </c>
       <c r="L42">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>4304.615386842248</v>
+        <v>4304.6153868422671</v>
       </c>
       <c r="M42">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9245,11 +10379,11 @@
       </c>
       <c r="O42">
         <f>MIN(Таблица5[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
-        <v>4304.615386842248</v>
+        <v>4304.6153868422671</v>
       </c>
       <c r="P42">
         <f>Таблица5[[#This Row],[err]]^2</f>
-        <v>18529713.628639035</v>
+        <v>18529713.628639199</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -9264,7 +10398,7 @@
       </c>
       <c r="L43">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>5192.6153912018872</v>
+        <v>5192.6153912019054</v>
       </c>
       <c r="M43">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9276,11 +10410,11 @@
       </c>
       <c r="O43">
         <f>MIN(Таблица5[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
-        <v>5192.6153912018872</v>
+        <v>5192.6153912019054</v>
       </c>
       <c r="P43">
         <f>Таблица5[[#This Row],[err]]^2</f>
-        <v>26963254.600946728</v>
+        <v>26963254.600946918</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
@@ -9295,7 +10429,7 @@
       </c>
       <c r="L44">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>5211.6153911778747</v>
+        <v>5211.6153911778929</v>
       </c>
       <c r="M44">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9307,11 +10441,11 @@
       </c>
       <c r="O44">
         <f>MIN(Таблица5[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
-        <v>5211.6153911778747</v>
+        <v>5211.6153911778929</v>
       </c>
       <c r="P44">
         <f>Таблица5[[#This Row],[err]]^2</f>
-        <v>27160934.985562112</v>
+        <v>27160934.985562302</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -9326,7 +10460,7 @@
       </c>
       <c r="L45">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>5331.6154026444892</v>
+        <v>5331.6154026445074</v>
       </c>
       <c r="M45">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9338,11 +10472,11 @@
       </c>
       <c r="O45">
         <f>MIN(Таблица5[[#This Row],[Расстояние от m1]:[Расстояние от m2]])</f>
-        <v>5331.6154026444892</v>
+        <v>5331.6154026445074</v>
       </c>
       <c r="P45">
         <f>Таблица5[[#This Row],[err]]^2</f>
-        <v>28426122.801715959</v>
+        <v>28426122.801716153</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
@@ -9357,7 +10491,7 @@
       </c>
       <c r="L46">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>18525.615390364659</v>
+        <v>18525.615390364677</v>
       </c>
       <c r="M46">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9388,7 +10522,7 @@
       </c>
       <c r="L47">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>19697.61541321945</v>
+        <v>19697.615413219468</v>
       </c>
       <c r="M47">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9419,7 +10553,7 @@
       </c>
       <c r="L48">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>22241.615391704017</v>
+        <v>22241.615391704039</v>
       </c>
       <c r="M48">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9438,7 +10572,7 @@
         <v>7377199.3324999921</v>
       </c>
     </row>
-    <row r="49" spans="9:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="9:20" x14ac:dyDescent="0.25">
       <c r="I49" s="4" t="s">
         <v>160</v>
       </c>
@@ -9450,7 +10584,7 @@
       </c>
       <c r="L49">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>24538.615403454187</v>
+        <v>24538.615403454205</v>
       </c>
       <c r="M49">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9469,7 +10603,7 @@
         <v>175644.81249999875</v>
       </c>
     </row>
-    <row r="50" spans="9:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="9:20" x14ac:dyDescent="0.25">
       <c r="I50" s="4" t="s">
         <v>125</v>
       </c>
@@ -9481,7 +10615,7 @@
       </c>
       <c r="L50">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>25457.61540674754</v>
+        <v>25457.615406747558</v>
       </c>
       <c r="M50">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9500,7 +10634,7 @@
         <v>249900.03250000146</v>
       </c>
     </row>
-    <row r="51" spans="9:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="9:20" x14ac:dyDescent="0.25">
       <c r="I51" s="4" t="s">
         <v>62</v>
       </c>
@@ -9512,7 +10646,7 @@
       </c>
       <c r="L51">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>26032.615395754117</v>
+        <v>26032.615395754136</v>
       </c>
       <c r="M51">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9531,7 +10665,7 @@
         <v>1155410.0325000032</v>
       </c>
     </row>
-    <row r="52" spans="9:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="9:20" x14ac:dyDescent="0.25">
       <c r="I52" s="4" t="s">
         <v>114</v>
       </c>
@@ -9543,7 +10677,7 @@
       </c>
       <c r="L52">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>26293.615437113109</v>
+        <v>26293.615437113127</v>
       </c>
       <c r="M52">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9562,7 +10696,7 @@
         <v>1784629.372500004</v>
       </c>
     </row>
-    <row r="53" spans="9:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="9:20" x14ac:dyDescent="0.25">
       <c r="I53" s="4" t="s">
         <v>50</v>
       </c>
@@ -9574,7 +10708,7 @@
       </c>
       <c r="L53">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>26702.615390519775</v>
+        <v>26702.615390519793</v>
       </c>
       <c r="M53">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9593,7 +10727,7 @@
         <v>3044676.132500005</v>
       </c>
     </row>
-    <row r="54" spans="9:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="9:20" x14ac:dyDescent="0.25">
       <c r="I54" s="5" t="s">
         <v>238</v>
       </c>
@@ -9605,7 +10739,7 @@
       </c>
       <c r="L54">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>29695.615403588959</v>
+        <v>29695.615403588974</v>
       </c>
       <c r="M54">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9624,7 +10758,7 @@
         <v>22447696.432500012</v>
       </c>
     </row>
-    <row r="55" spans="9:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="9:20" x14ac:dyDescent="0.25">
       <c r="I55" s="4" t="s">
         <v>38</v>
       </c>
@@ -9636,7 +10770,7 @@
       </c>
       <c r="L55">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$58)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$58)^2)</f>
-        <v>30391.615399826096</v>
+        <v>30391.615399826114</v>
       </c>
       <c r="M55">
         <f>SQRT((Таблица5[[#This Row],[GDP per capita (USD)]]-$J$59)^2 + (Таблица5[[#This Row],[  Life satisfaction]]-$K$59)^2)</f>
@@ -9654,31 +10788,64 @@
         <f>Таблица5[[#This Row],[err]]^2</f>
         <v>29527269.212500017</v>
       </c>
+      <c r="S55" t="s">
+        <v>270</v>
+      </c>
+      <c r="T55" t="s">
+        <v>271</v>
+      </c>
     </row>
-    <row r="57" spans="9:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="9:20" x14ac:dyDescent="0.25">
+      <c r="R56">
+        <v>1</v>
+      </c>
+      <c r="S56">
+        <f>SUM(J33:J45) / COUNT(J33:J45)</f>
+        <v>28833.384615384617</v>
+      </c>
+      <c r="T56">
+        <f>SUM(K33:K45) / COUNT(K33:K45)</f>
+        <v>6.2384615384615376</v>
+      </c>
+    </row>
+    <row r="57" spans="9:20" x14ac:dyDescent="0.25">
       <c r="J57" t="s">
         <v>265</v>
       </c>
       <c r="K57" t="s">
         <v>266</v>
       </c>
+      <c r="O57" t="s">
+        <v>269</v>
+      </c>
       <c r="P57">
         <f>SUM(Таблица5[err^2])</f>
-        <v>364039280.49269235</v>
+        <v>364039280.49269229</v>
+      </c>
+      <c r="R57">
+        <v>2</v>
+      </c>
+      <c r="S57">
+        <f>SUM(J46:J55) / COUNT(J46:J55)</f>
+        <v>53791.1</v>
+      </c>
+      <c r="T57">
+        <f>SUM(K46:K55) / COUNT(K46:K55)</f>
+        <v>7.15</v>
       </c>
     </row>
-    <row r="58" spans="9:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="9:20" x14ac:dyDescent="0.25">
       <c r="I58" t="s">
         <v>263</v>
       </c>
       <c r="J58">
-        <v>28833.384615384617</v>
+        <v>28833.384615384599</v>
       </c>
       <c r="K58">
         <v>6.2384615384615376</v>
       </c>
     </row>
-    <row r="59" spans="9:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="9:20" x14ac:dyDescent="0.25">
       <c r="I59" t="s">
         <v>264</v>
       </c>
